--- a/AAII_Financials/Quarterly/MHK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MHK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="92">
   <si>
     <t>MHK</t>
   </si>
@@ -656,540 +656,552 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46207</v>
+      </c>
+      <c r="E7" s="2">
         <v>46116</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45927</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45836</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45745</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45563</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45472</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45381</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45108</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45017</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44835</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44744</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44653</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44471</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44380</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44289</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44009</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43918</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43736</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43645</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43554</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43372</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42917</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42826</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2991400</v>
+      </c>
+      <c r="E8" s="3">
         <v>2728700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2699700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2757900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2802100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2525800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2637200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2719000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2801300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2679400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2612300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2766100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2950500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2806200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2650700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2917500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3153200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3015700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2760700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2817000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2953800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2669000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2641800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2574900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2049800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2285800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2424500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2519200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2584500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2442500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2448600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2545800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2577000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2412200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2369100</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2448500</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2453000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2220600</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2182600</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>2294100</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2169300</v>
+      </c>
+      <c r="E9" s="3">
         <v>2052000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2031300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2058900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2061500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1917300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1993900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2010000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2042300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2024400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1963400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2031400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2188100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2133700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2060300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2173500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2279300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2212600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2020900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1979200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2046300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1867100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1880800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1851000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1629800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1657500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1759300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1820000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1842000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1785000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1791900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1815200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1798400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1693000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1604100</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1656400</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1660900</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1537500</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1479300</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>1550100</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>822100</v>
+      </c>
+      <c r="E10" s="3">
         <v>676700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>668400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>699000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>740600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>608500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>643300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>709000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>759000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>655000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>648900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>734700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>762400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>672500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>590400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>744000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>873900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>803100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>739800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>837900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>907500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>801900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>761000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>723900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>420000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>628300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>665200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>699200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>742500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>657500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>656700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>730600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>778600</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>719200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>765000</v>
-      </c>
-      <c r="AL10" s="3">
-        <v>792100</v>
       </c>
       <c r="AM10" s="3">
         <v>792100</v>
       </c>
       <c r="AN10" s="3">
+        <v>792100</v>
+      </c>
+      <c r="AO10" s="3">
         <v>683100</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>703300</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>744000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1232,8 +1244,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1354,8 +1367,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1476,175 +1492,181 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E14" s="3">
         <v>37600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>122300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>47100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>29400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>25300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>43500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>19500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>41400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>7900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>104600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>923200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>41700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>32200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>43400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>730300</v>
-      </c>
-      <c r="S14" s="3">
-        <v>1900</v>
       </c>
       <c r="T14" s="3">
         <v>1900</v>
       </c>
       <c r="U14" s="3">
+        <v>1900</v>
+      </c>
+      <c r="V14" s="3">
         <v>4600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>6800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>11200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>26100</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>26500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>67200</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>12700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>41800</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>74700</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>8900</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>35700</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>20600</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>19900</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>16000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>22100</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>15200</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>13900</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>15900</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>4000</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>16200</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>21300</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>159300</v>
+      </c>
+      <c r="E15" s="3">
         <v>181800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>176300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>170300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>155600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>150400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>156400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>156200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>171500</v>
-      </c>
-      <c r="L15" s="3">
-        <v>154200</v>
       </c>
       <c r="M15" s="3">
         <v>154200</v>
       </c>
       <c r="N15" s="3">
+        <v>154200</v>
+      </c>
+      <c r="O15" s="3">
         <v>149600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>156600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>169900</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1690,8 +1712,8 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-      <c r="AG15" s="3" t="s">
-        <v>8</v>
+      <c r="AG15" s="3">
+        <v>0</v>
       </c>
       <c r="AH15" s="3" t="s">
         <v>8</v>
@@ -1702,8 +1724,8 @@
       <c r="AJ15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK15" s="3">
-        <v>0</v>
+      <c r="AK15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AL15" s="3">
         <v>0</v>
@@ -1720,8 +1742,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1761,252 +1786,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2698700</v>
+      </c>
+      <c r="E17" s="3">
         <v>2579300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2509100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2574100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2584000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2404500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2473100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2487200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2545900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2524900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2340600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2576600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2755700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2648300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2589600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3423100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2785300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2694900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2507600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2457000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2549400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2351500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2359000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2312100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2114400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2134300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2264400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2344100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2317600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2277200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2235200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2258600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2250700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2143800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2025600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2068400</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2097200</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1945900</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1877300</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>1915800</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>292700</v>
+      </c>
+      <c r="E18" s="3">
         <v>149400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>190600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>183800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>218100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>121300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>164100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>231800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>255400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>154500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>271700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>189500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>194800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>157900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>61100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-505600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>367900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>320800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>253100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>360000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>404400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>317500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>282800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>262800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-64600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>151500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>160100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>175100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>266900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>165300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>213400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>287200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>326300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>268400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>343500</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>380100</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>355800</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>274700</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>305300</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>378300</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2049,618 +2081,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>400</v>
+      </c>
+      <c r="E20" s="3">
         <v>1200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-8500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-10000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1100</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>11200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>6700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>2600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-5700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>4300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>12400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>3000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>3700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-2100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-4000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-3800</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>2900</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>3200</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-3800</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>451600</v>
+      </c>
+      <c r="E21" s="3">
         <v>330000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>365800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>354500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>370700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>272200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>318300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>388700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>425300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>309800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>429800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>347600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>349200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>328400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>210100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-350900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>512300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>459800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>395400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>508600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>564100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>471000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>446000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>414800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>92100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>291300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>318100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>332400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>410400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>306400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>352000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>419500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>451300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>387100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>458100</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>492300</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>462600</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>382600</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>412800</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>478100</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E22" s="3">
         <v>2400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>5000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>5200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>6400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>9900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>11200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>12600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>14900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>17400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>20100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>22900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>17100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>14600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>13800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>12100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>11500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>12200</v>
-      </c>
-      <c r="V22" s="3">
-        <v>14900</v>
       </c>
       <c r="W22" s="3">
         <v>14900</v>
       </c>
       <c r="X22" s="3">
+        <v>14900</v>
+      </c>
+      <c r="Y22" s="3">
         <v>15200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>15900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>14900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>13000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>8700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>11000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>9300</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>10500</v>
       </c>
       <c r="AF22" s="3">
         <v>10500</v>
       </c>
       <c r="AG22" s="3">
+        <v>10500</v>
+      </c>
+      <c r="AH22" s="3">
         <v>14400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>9000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>7900</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>7500</v>
-      </c>
-      <c r="AK22" s="3">
-        <v>7300</v>
       </c>
       <c r="AL22" s="3">
         <v>7300</v>
       </c>
       <c r="AM22" s="3">
+        <v>7300</v>
+      </c>
+      <c r="AN22" s="3">
         <v>8400</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>8200</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>8500</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>248500</v>
+      </c>
+      <c r="E23" s="3">
         <v>108200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>66000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>132100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>180500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>90100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>108500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>201800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>199800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>132800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>153600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-745300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>128000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>109200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>36500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-518100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>358700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>306900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>239800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>345000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>400700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>304500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>273600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>248600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-75000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>137100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>153400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>178200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>259400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>158600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>198500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>277500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>316400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>256900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>332500</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>371600</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>344400</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>269400</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>300000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>365100</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>52300</v>
+      </c>
+      <c r="E24" s="3">
         <v>-8900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>24000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>23300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>34000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>17500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>18300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>39800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>42300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>27800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>14200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>15000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>26800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>28900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>15600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>78200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>61400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>50700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>73800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>64200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>67700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>25200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>43200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-26400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>26700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-111300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>22500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>56700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>37000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-59800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>49500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>118800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>47600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>46300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>100500</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>82700</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>68400</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>65500</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>94200</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2781,252 +2829,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>196200</v>
+      </c>
+      <c r="E26" s="3">
         <v>117100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>42000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>108800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>146500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>72600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>90200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>162000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>157500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>105000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>139400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-760300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>101200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>80300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>33600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-533700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>280500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>245400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>189100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>271200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>336500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>236800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>248400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>205500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-48600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>110500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>264700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>155700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>202700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>121600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>258200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>228000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>197500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>209200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>286100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>271000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>261700</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>201100</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>234500</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>270800</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>196100</v>
+      </c>
+      <c r="E27" s="3">
         <v>117100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>42000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>108800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>146500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>72600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>90200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>162000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>157400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>105000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>139500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-760400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>101200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>80200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>33500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-534000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>280400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>245300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>189100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>271000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>336300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>236800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>248200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>205100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-48300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>110500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>264700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>155500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>202400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>121600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>254600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>226300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>196600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>208500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>285600</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>270000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>260700</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>200600</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>233700</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3147,8 +3204,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3191,8 +3251,8 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>8</v>
@@ -3200,8 +3260,8 @@
       <c r="S29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
+      <c r="T29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U29" s="3">
         <v>0</v>
@@ -3221,17 +3281,17 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="3" t="s">
+      <c r="AC29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -3239,11 +3299,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-28200</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
@@ -3251,11 +3311,11 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-45200</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
@@ -3269,8 +3329,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3391,8 +3454,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3513,252 +3579,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>8500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>10000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-11200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-6700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>5700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-4300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-12400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-3700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>2100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>4000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>3800</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>1300</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>3000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-3200</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>196100</v>
+      </c>
+      <c r="E33" s="3">
         <v>117100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>42000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>108800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>146500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>72600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>90200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>162000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>157400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>105000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>139500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-760400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>101200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>80200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>33500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-534000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>280400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>245300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>189100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>271000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>336300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>236800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>248200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>205100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-48300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>110500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>264700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>155500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>202400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>121600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>226400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>226300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>196600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>208500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>240400</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>270000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>260700</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>200600</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>233700</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3879,257 +3954,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>196100</v>
+      </c>
+      <c r="E35" s="3">
         <v>117100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>42000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>108800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>146500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>72600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>90200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>162000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>157400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>105000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>139500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-760400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>101200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>80200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>33500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-534000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>280400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>245300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>189100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>271000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>336300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>236800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>248200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>205100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-48300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>110500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>264700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>155500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>202400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>121600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>226400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>226300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>196600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>208500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>240400</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>270000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>260700</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>200600</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>233700</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46207</v>
+      </c>
+      <c r="E38" s="2">
         <v>46116</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45927</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45836</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45745</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45563</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45472</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45381</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45108</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45017</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44835</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44744</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44653</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44471</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44380</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44289</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44009</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43918</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43736</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43645</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43554</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43372</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42917</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42826</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4172,8 +4256,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4216,130 +4301,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>849600</v>
+      </c>
+      <c r="E41" s="3">
         <v>872300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>856100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>516200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>546700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>702500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>666600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>424000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>497400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>658500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>642600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>518500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>570900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>572900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>509600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>327000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>224000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>230600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>268900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1128000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>753700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>557300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>768600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>781200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>737700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>263100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>134800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>111300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>128100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>105700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>119100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>91400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>518200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>114800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>84900</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>84500</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>130200</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>188400</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>121700</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>112100</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4380,40 +4469,40 @@
         <v>0</v>
       </c>
       <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
         <v>150000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>158000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>110000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>265000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>310000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>323000</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
-      </c>
       <c r="W42" s="3">
+        <v>0</v>
+      </c>
+      <c r="X42" s="3">
         <v>662400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>782300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>571700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>407800</v>
-      </c>
-      <c r="AA42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB42" s="3" t="s">
         <v>8</v>
@@ -4430,8 +4519,8 @@
       <c r="AF42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG42" s="3">
-        <v>0</v>
+      <c r="AG42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH42" s="3">
         <v>0</v>
@@ -4460,496 +4549,511 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2284300</v>
+      </c>
+      <c r="E43" s="3">
         <v>2092700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1924100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2249600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2254800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2129700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1762100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2043400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2018500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2007200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1874700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1943100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2087100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2052400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1904800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2003300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2105800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2044700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1840000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1880500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2017600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1813900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1709500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1711000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1586400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1644800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1526600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1787200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1819500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1743600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1606200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1755700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1737900</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1689900</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1558200</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1656100</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1639600</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1497900</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1376200</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1506300</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2585600</v>
+      </c>
+      <c r="E44" s="3">
         <v>2680500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2661700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2692900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2709900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2610400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2513600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2612100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2579900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2527700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2551900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2519700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2618700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2729900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2793800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2900100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2826000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2513200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2391700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2215600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2082000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1996600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1913000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1842000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1922000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2195400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2282300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2338000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2367600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2338100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2287600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2214300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>2061200</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>2045000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1948700</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1911000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1865900</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1740900</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>1675800</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>1673200</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E45" s="3">
         <v>10700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>13000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>32800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>18700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>23100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>22300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>20800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>16800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>15800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>19300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>22400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>22500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>21900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>528900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>514000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>519900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>466200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>414800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>421900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>434900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>416000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>400800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>410000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>499800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>509800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>485700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>491400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>493100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>501600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>496500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>487100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>456300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>447300</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>481300</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>345500</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>374900</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>307800</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>297900</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>284600</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6273900</v>
+      </c>
+      <c r="E46" s="3">
         <v>6200200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5967100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6007600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6064900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5977900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5454800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5621400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5641300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5721700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5604300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5504300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5851300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6061100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5895100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5854300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5940700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5564700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5238400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5646100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5950600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5566000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>5363700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>5152000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4746000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4613000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4429500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4727800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4808300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4689000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>4509300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>4548500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>4773700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>4297000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>4073000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>3997100</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>4010700</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>3735000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>3471500</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>3576300</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4992,8 +5096,8 @@
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -5070,252 +5174,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5028900</v>
+      </c>
+      <c r="E48" s="3">
         <v>5057200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5180700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5079900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5187900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5032100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4953900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5142900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5155400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5298700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5421700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5193300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5357600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5342000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5049000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4924900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4986800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4937400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5026800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4827900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4842700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4769900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>4914400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>4708300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>4752600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>4804200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>5021900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>4934700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>5058000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>4995200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>4699900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>4586200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>4421100</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>4460800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>4270800</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>4090100</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>3892300</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>3506200</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>3370300</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>3340900</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1983500</v>
+      </c>
+      <c r="E49" s="3">
         <v>1995800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2023500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2032900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2044600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1950000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1904000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2019300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1978100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1994000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2035000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1979900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2919000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2915500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2785700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2651100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3392700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3462900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3507900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3523500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3531900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3516600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3602400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3493400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3452700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3424000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3498900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3436200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3516300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3499600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3482800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3466800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>3305600</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>3412600</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>3363200</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>3344700</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>3295400</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>3128900</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>3109000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>3208500</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5436,8 +5549,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5558,8 +5674,11 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5602,86 +5721,89 @@
       <c r="P52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="Q52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R52" s="3">
         <v>390600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>370700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>369200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>421700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>451400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>452800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>467600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>437600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>447300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>430500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>418100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>415700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>436400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>294100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>423400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>421300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>407100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>399400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>393700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>389900</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>387900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>390900</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>391200</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>357500</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>279700</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>294900</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5802,130 +5924,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13823200</v>
+      </c>
+      <c r="E54" s="3">
         <v>13791100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>13687300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13620500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>13778800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>13408500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>12736500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>13313200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>13279600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>13531500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>13559800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>13138500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>14585200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>14763500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>14120400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>13801000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>14689500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>14386700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>14224500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>14450300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>14792800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>14290100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>14327800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>13784200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>13369400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>13256900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>13386700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>13392800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>13806100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>13605100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>13099100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>13000900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>12894000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>12560400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>12094900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>11822800</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>11589500</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>10727500</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>10230600</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>10420600</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5968,8 +6096,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6012,740 +6141,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1224800</v>
+      </c>
+      <c r="E57" s="3">
         <v>1205400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1088900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1187800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1173100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1124600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>978500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1061200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1082800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1101900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1038000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1082400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1184100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1211700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1094000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1217700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1359200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1296100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1228600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1147000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1131200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1064800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1016900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>989900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>845300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>899200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>825000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>964100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>976200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>914200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>811900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>925200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>951200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>897500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>810000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>859900</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>871400</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>780500</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>729400</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>767200</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>881400</v>
+      </c>
+      <c r="E58" s="3">
         <v>501100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>411700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>294800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>575000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>797900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>667900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>576900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>827900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1040800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1110600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1029100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1144100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1163000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>840600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1542100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1498900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1546500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>624500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>588700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>958800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>953900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>377300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>356100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>135400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1210500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1051500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1273200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1891500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1763300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1742400</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1333900</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1146500</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1331900</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1203700</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1172800</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>1754100</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>1498000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>1382700</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>1548300</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E59" s="3">
         <v>21200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>26000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>28600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>30000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>29600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>31000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>35100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>34400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>34500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>39800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>39200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>47100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>41200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1135700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1144900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1066300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1029100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1093200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1166100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1088900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>988600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>977100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1041100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>891600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>761600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>836100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>877400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>838000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>756700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>712000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>698200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>638400</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>566500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>641600</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>664300</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>595200</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>549900</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>606200</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>667800</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3275300</v>
+      </c>
+      <c r="E60" s="3">
         <v>2871300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2722100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2674400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2853200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2972400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2672300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2771000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2937700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3120100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3145900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3188600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3287900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3318400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3070300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3904700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3924400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3871600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2946400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2901700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3178900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3007300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2371200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2387100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1872200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2871300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2712600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3114700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3705800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>3434200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>3266200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2957300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2736100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2795900</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2655400</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>2697000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>3220700</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>2828300</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>2718300</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>2983300</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1477300</v>
+      </c>
+      <c r="E61" s="3">
         <v>2022400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2045600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2043300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2054100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1990300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1960400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2014400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1993100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2016300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2039300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1990600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2323900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2569300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1978600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1020000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1052100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1088400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1700300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1710200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1723300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1719100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2356900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2282800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2573200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1514000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1518400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1483600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1169500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1498000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1515600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1528600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1884000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1585700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1559900</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1544700</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>1174400</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>1132300</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>1128700</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>1165600</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>359500</v>
+      </c>
+      <c r="E62" s="3">
         <v>346600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>355500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>345900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>334400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>340400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>333800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>343900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>335100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>361500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>348000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>340300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>356100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>341400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1053700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1051200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1106100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1139100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1149700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1085900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1116700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1064600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1058500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>947300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>999200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1024000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1029300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1029200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1109200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1095800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>877200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>912100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>870500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>801900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>783100</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>755000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>713100</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>677900</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>576300</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>574300</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6866,8 +7014,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6988,8 +7139,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7110,130 +7264,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5278500</v>
+      </c>
+      <c r="E66" s="3">
         <v>5411400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5308600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5279500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5481200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5546600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5221700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5457500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5627100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5883700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5930700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5867100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6373100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6657800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>6108900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5982300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>6088900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>6105700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5803100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5704800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>6025700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5797600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5793400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5623600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5450600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>5415600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>5266800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>5634000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>5991000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>6034300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>5665300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>5437200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>5528500</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>5222400</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>5035700</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>5033800</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>5143000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>4670100</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>4454100</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>4755200</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7276,8 +7436,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7398,8 +7559,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7520,8 +7684,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7642,8 +7809,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7764,130 +7934,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7691700</v>
+      </c>
+      <c r="E72" s="3">
         <v>7555600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7503100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7544300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7476100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7372200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7283000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7306800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7144800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7075200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6970200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6830800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7591200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7490000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7409800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7376300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7910700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7630800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>7692100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>7930000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>7867800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>7673100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>7559200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>7430900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>7225800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>7274100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>7232300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>6991100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>6903300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>6709800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>6588200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>6635900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>6409600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>6213000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>6004500</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>5764100</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>5494100</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>5233500</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>5032900</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>4799200</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8008,8 +8184,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8130,8 +8309,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8252,130 +8434,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8540700</v>
+      </c>
+      <c r="E76" s="3">
         <v>8375600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8373300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8335600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8292100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7856100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7509300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7849500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7646500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7641900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7623100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7265500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8206100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8099500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8011500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7818800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8600600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8281000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>8421400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>8745500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>8767100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>8492400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>8534300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>8160700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>7918800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>7841400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>8119800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>7758800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>7815100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>7570800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>7433800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>7563800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>7365600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>7337900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>7059200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>6789100</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>6446500</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>6057400</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>5776500</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>5665400</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8496,257 +8684,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46207</v>
+      </c>
+      <c r="E80" s="2">
         <v>46116</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45927</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45836</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45745</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45563</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45472</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45381</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45108</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45017</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44835</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44744</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44653</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44471</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44380</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44289</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44009</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43918</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43736</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43645</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43554</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43372</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42917</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42826</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>196100</v>
+      </c>
+      <c r="E81" s="3">
         <v>117100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>42000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>108800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>146500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>72600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>90200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>162000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>157400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>105000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>139500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-760400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>101200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>80200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>33500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-534000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>280400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>245300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>189100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>271000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>336300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>236800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>248200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>205100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-48300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>110500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>264700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>155500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>202400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>121600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>226400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>226300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>196600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>208500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>240400</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>270000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>260700</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>200600</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>233700</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8789,130 +8986,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>148400</v>
+      </c>
+      <c r="E83" s="3">
         <v>143800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>149500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>149200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>164800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>147200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>267500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>142600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>149600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>162700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>151800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>146500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>134700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>134200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>159000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>153500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>141600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>141400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>143400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>148600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>148500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>151200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>156600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>151300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>154100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>145500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>153800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>144900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>140500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>137300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>139100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>133000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>127000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>122700</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>118400</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>113500</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>109800</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>105000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>104400</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>103700</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9033,8 +9234,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9155,8 +9359,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9277,8 +9484,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9399,8 +9609,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9521,130 +9734,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>316500</v>
+      </c>
+      <c r="E89" s="3">
         <v>110100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>459600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>386600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>206300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>397000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>319600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>233600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>183700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>296300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>512000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>263600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>257300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>241700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>224800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>147700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>55000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>212400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>498700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>338400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>259600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>407800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>598500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>568500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>195000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>440700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>411800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>396200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>170100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>286900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>273500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>437800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>183200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>319400</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>460300</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>248000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>165900</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>342900</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>419900</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9687,130 +9906,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-88300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-102300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-194400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-76300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-80200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-89100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-160800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-115400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-91400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-86800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-240300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-127400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-116700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-128500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-150700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-150000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-150600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-129500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-300900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-147700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-112700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-114700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-160100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-69100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-80600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-115600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-139800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-124600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-144100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-136900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-151200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-144600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-247400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-250900</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-251400</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-229200</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-224200</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-201300</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-211400</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>93100</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9931,8 +10154,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10053,130 +10279,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-85000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-102300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-196300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-76300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-80200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-89100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-160800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-115400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-91400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-86800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-240300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-127400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>37300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-639900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-251000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-153300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-105600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-115500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-670700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>442500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>4800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-333300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-324100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-420200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-77000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-133400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-141600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-120600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-142100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-211800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-303900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-542500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-244400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-241400</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-335300</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-229500</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-473800</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-202100</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-211400</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-183800</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10219,8 +10451,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10263,8 +10496,8 @@
       <c r="P96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10341,8 +10574,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10463,8 +10699,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10585,8 +10824,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10707,370 +10949,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-259700</v>
+      </c>
+      <c r="E100" s="3">
         <v>11800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>62400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-327300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-295900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>90800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>22100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-270100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-305400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-76100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>63200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-430100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-294700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>451000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>197300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>39900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-51800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>9000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-397300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-559200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-155600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-120200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-119100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-132000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-24200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>87200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-279600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-304900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-232200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>26800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>46500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-156500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>221400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>86600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>16300</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-280600</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>166400</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>90900</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-122700</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-251900</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E101" s="3">
         <v>30500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-15700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-7500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-4900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>4900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-6900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-8200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-5100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-5400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-8400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>3100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>13300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-5400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-8400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>3100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>13300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-3500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-7700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>8900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-17500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>22800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-2700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>7400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-20400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>4000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-3100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>1500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-1800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-1400</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-11400</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>1600</v>
       </c>
-      <c r="AK101" s="3">
-        <v>0</v>
-      </c>
       <c r="AL101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM101" s="3">
         <v>4100</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>1200</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>12100</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>700</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-22700</v>
+      </c>
+      <c r="E102" s="3">
         <v>16200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>339900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-30500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-155800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>35900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>242600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-73400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-161100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>15900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>124100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-52400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>63300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>182700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>103000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-6600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-38300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-859100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>374400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>196400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-211400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-12600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>43500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>474600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>128300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>23500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-16800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>22400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-13400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>27700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-426900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>403400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>30000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>400</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-45700</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-58200</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>66800</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>9600</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>100</v>
       </c>
     </row>
